--- a/5. feature_catalog.xlsx
+++ b/5. feature_catalog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linh\Desktop\Growth &amp; Experimentation Project for Ride-Hailing Promotions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D0B8F6-1F38-42C8-A946-E1D3ACE46B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB780F7F-AC77-4883-B791-B22AA1BCCCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="100">
   <si>
     <t>Tên Feature</t>
   </si>
@@ -112,9 +112,6 @@
     <t>Có thuộc giờ cao điểm hay không</t>
   </si>
   <si>
-    <t>7-9h và 16-19h</t>
-  </si>
-  <si>
     <t>Phân tích giờ cao điểm</t>
   </si>
   <si>
@@ -308,13 +305,28 @@
   </si>
   <si>
     <t>Object</t>
+  </si>
+  <si>
+    <t>Tạo các khoảng giờ cao điểm</t>
+  </si>
+  <si>
+    <t>time_bucket</t>
+  </si>
+  <si>
+    <t>Khung giờ gộp</t>
+  </si>
+  <si>
+    <t>morning(6-9), midday(10-15), evening(16-21), late_night(22-5)</t>
+  </si>
+  <si>
+    <t>ĐƠN VỊ cho segmentation &amp; experiment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +342,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -339,7 +355,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -362,11 +378,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -374,6 +401,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -677,8 +711,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" customWidth="1"/>
@@ -686,11 +720,11 @@
     <col min="4" max="4" width="28.109375" customWidth="1"/>
     <col min="5" max="5" width="12.109375" customWidth="1"/>
     <col min="6" max="6" width="28.109375" customWidth="1"/>
-    <col min="7" max="7" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="37.77734375" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="24.6" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -713,7 +747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -736,7 +770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -759,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -782,7 +816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -805,7 +839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -822,353 +856,376 @@
         <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>94</v>
+    </row>
+    <row r="22" spans="1:7" ht="25.8" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
